--- a/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0001T0006Z000C1N3_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0001T0006Z000C1N3_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>19.09101041551168</v>
+        <v>3.102289192520647</v>
       </c>
       <c r="D2" t="n">
-        <v>20.18412161656035</v>
+        <v>3.279919762691057</v>
       </c>
       <c r="E2" t="n">
-        <v>14.62761213897431</v>
+        <v>2.376986972583326</v>
       </c>
       <c r="F2" t="n">
-        <v>15.0843074557394</v>
+        <v>2.451199961557652</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>22.14950111436841</v>
+        <v>3.599293931084867</v>
       </c>
       <c r="D3" t="n">
-        <v>20.8921540001368</v>
+        <v>3.394975025022231</v>
       </c>
       <c r="E3" t="n">
-        <v>14.62761213897431</v>
+        <v>2.376986972583326</v>
       </c>
       <c r="F3" t="n">
-        <v>15.0843074557394</v>
+        <v>2.451199961557652</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>8.781897143833158</v>
+        <v>1.427058285872888</v>
       </c>
       <c r="D4" t="n">
-        <v>8.439911063834259</v>
+        <v>1.371485547873067</v>
       </c>
       <c r="E4" t="n">
-        <v>14.62761213897431</v>
+        <v>2.376986972583326</v>
       </c>
       <c r="F4" t="n">
-        <v>15.0843074557394</v>
+        <v>2.451199961557652</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>11.15210776236494</v>
+        <v>1.812217511384303</v>
       </c>
       <c r="D5" t="n">
-        <v>11.6986067261678</v>
+        <v>1.901023593002268</v>
       </c>
       <c r="E5" t="n">
-        <v>14.62761213897431</v>
+        <v>2.376986972583326</v>
       </c>
       <c r="F5" t="n">
-        <v>15.0843074557394</v>
+        <v>2.451199961557652</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>34.06110008720052</v>
+        <v>5.534928764170085</v>
       </c>
       <c r="D6" t="n">
-        <v>35.49513094760539</v>
+        <v>5.767958778985876</v>
       </c>
       <c r="E6" t="n">
-        <v>14.62761213897431</v>
+        <v>2.376986972583326</v>
       </c>
       <c r="F6" t="n">
-        <v>15.0843074557394</v>
+        <v>2.451199961557652</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>43.92540871483774</v>
+        <v>7.137878916161132</v>
       </c>
       <c r="D7" t="n">
-        <v>45.3613119499326</v>
+        <v>7.371213191864047</v>
       </c>
       <c r="E7" t="n">
-        <v>14.62761213897431</v>
+        <v>2.376986972583326</v>
       </c>
       <c r="F7" t="n">
-        <v>15.0843074557394</v>
+        <v>2.451199961557652</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>46.68858560213527</v>
+        <v>7.586895160346981</v>
       </c>
       <c r="D8" t="n">
-        <v>48.04819890256761</v>
+        <v>7.807832321667236</v>
       </c>
       <c r="E8" t="n">
-        <v>14.62761213897431</v>
+        <v>2.376986972583326</v>
       </c>
       <c r="F8" t="n">
-        <v>15.0843074557394</v>
+        <v>2.451199961557652</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>7.61346263836606</v>
+        <v>1.237187678734485</v>
       </c>
       <c r="D9" t="n">
-        <v>7.520511648436406</v>
+        <v>1.222083142870916</v>
       </c>
       <c r="E9" t="n">
-        <v>14.62761213897431</v>
+        <v>2.376986972583326</v>
       </c>
       <c r="F9" t="n">
-        <v>15.0843074557394</v>
+        <v>2.451199961557652</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>12.96478086518184</v>
+        <v>2.106776890592049</v>
       </c>
       <c r="D10" t="n">
-        <v>12.81504734335899</v>
+        <v>2.082445193295837</v>
       </c>
       <c r="E10" t="n">
-        <v>14.62761213897431</v>
+        <v>2.376986972583326</v>
       </c>
       <c r="F10" t="n">
-        <v>15.0843074557394</v>
+        <v>2.451199961557652</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>3.266830043539395</v>
+        <v>0.5308598820751517</v>
       </c>
       <c r="D11" t="n">
-        <v>3.259038761273555</v>
+        <v>0.5295937987069528</v>
       </c>
       <c r="E11" t="n">
-        <v>14.62761213897431</v>
+        <v>2.376986972583326</v>
       </c>
       <c r="F11" t="n">
-        <v>15.0843074557394</v>
+        <v>2.451199961557652</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>23.9574992931683</v>
+        <v>3.893093635139849</v>
       </c>
       <c r="D12" t="n">
-        <v>24.05793233916251</v>
+        <v>3.909414005113907</v>
       </c>
       <c r="E12" t="n">
-        <v>14.62761213897431</v>
+        <v>2.376986972583326</v>
       </c>
       <c r="F12" t="n">
-        <v>15.0843074557394</v>
+        <v>2.451199961557652</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>41.97234656584273</v>
+        <v>6.820506316949444</v>
       </c>
       <c r="D13" t="n">
-        <v>42.02113694478734</v>
+        <v>6.828434753527944</v>
       </c>
       <c r="E13" t="n">
-        <v>14.62761213897431</v>
+        <v>2.376986972583326</v>
       </c>
       <c r="F13" t="n">
-        <v>15.0843074557394</v>
+        <v>2.451199961557652</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
